--- a/xlsx/tests/docs/ERFC-PRECISE.xlsx
+++ b/xlsx/tests/docs/ERFC-PRECISE.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve\Documents\IronCalc work\IronCalc-clone\IronCalc-SF\xlsx\tests\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc/xlsx/tests/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9D2D6A-D263-406A-B3A5-63CEB854E82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9019F7-1D3B-EA48-9FD3-848C66C671E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BC44EA43-B61B-417F-9ADF-F059B85B51E3}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29040" windowHeight="15720" xr2:uid="{BC44EA43-B61B-417F-9ADF-F059B85B51E3}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ERFC.PRECISE" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -73,7 +73,7 @@
     <numFmt numFmtId="164" formatCode="0.000000000000000"/>
     <numFmt numFmtId="165" formatCode="0.0000000000000000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,18 +84,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -110,19 +121,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -459,38 +484,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFC17462-0B08-4BD1-9C6A-0FDADCE81763}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.140625" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="23.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.1640625" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="23.5" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
         <v>-5</v>
       </c>
       <c r="B2" s="3">
         <f>_xlfn.ERFC.PRECISE($A2)</f>
         <v>1.9999999999984626</v>
       </c>
-      <c r="C2" s="1" t="str">
+      <c r="C2" s="2" t="str">
         <f t="shared" ref="C2:C6" ca="1" si="0">_xlfn.FORMULATEXT($B2)</f>
         <v>=ERFC.PRECISE($A2)</v>
       </c>
@@ -498,8 +523,8 @@
         <v>1.9999999999984599</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
         <f>A2+0.5</f>
         <v>-4.5</v>
       </c>
@@ -507,7 +532,7 @@
         <f>_xlfn.ERFC.PRECISE($A3)</f>
         <v>1.9999999998033839</v>
       </c>
-      <c r="C3" s="1" t="str">
+      <c r="C3" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>=ERFC.PRECISE($A3)</v>
       </c>
@@ -515,8 +540,8 @@
         <v>1.9999999998033799</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
         <f t="shared" ref="A4:A22" si="1">A3+0.5</f>
         <v>-4</v>
       </c>
@@ -524,7 +549,7 @@
         <f t="shared" ref="B4:B16" si="2">_xlfn.ERFC.PRECISE($A4)</f>
         <v>1.9999999845827421</v>
       </c>
-      <c r="C4" s="1" t="str">
+      <c r="C4" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>=ERFC.PRECISE($A4)</v>
       </c>
@@ -532,8 +557,8 @@
         <v>1.9999999845827401</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
         <f t="shared" si="1"/>
         <v>-3.5</v>
       </c>
@@ -541,7 +566,7 @@
         <f t="shared" si="2"/>
         <v>1.9999992569016276</v>
       </c>
-      <c r="C5" s="1" t="str">
+      <c r="C5" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>=ERFC.PRECISE($A5)</v>
       </c>
@@ -549,8 +574,8 @@
         <v>1.9999992569016201</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
         <f t="shared" si="1"/>
         <v>-3</v>
       </c>
@@ -558,7 +583,7 @@
         <f t="shared" si="2"/>
         <v>1.9999779095030015</v>
       </c>
-      <c r="C6" s="1" t="str">
+      <c r="C6" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>=ERFC.PRECISE($A6)</v>
       </c>
@@ -566,8 +591,8 @@
         <v>1.9999779095029999</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <f t="shared" si="1"/>
         <v>-2.5</v>
       </c>
@@ -575,7 +600,7 @@
         <f t="shared" si="2"/>
         <v>1.999593047982555</v>
       </c>
-      <c r="C7" s="1" t="str">
+      <c r="C7" s="2" t="str">
         <f ca="1">_xlfn.FORMULATEXT($B7)</f>
         <v>=ERFC.PRECISE($A7)</v>
       </c>
@@ -583,8 +608,8 @@
         <v>1.9995930479825501</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
         <f t="shared" si="1"/>
         <v>-2</v>
       </c>
@@ -592,7 +617,7 @@
         <f t="shared" si="2"/>
         <v>1.9953222650189528</v>
       </c>
-      <c r="C8" s="1" t="str">
+      <c r="C8" s="2" t="str">
         <f t="shared" ref="C8:C22" ca="1" si="3">_xlfn.FORMULATEXT($B8)</f>
         <v>=ERFC.PRECISE($A8)</v>
       </c>
@@ -600,8 +625,8 @@
         <v>1.9953222650189999</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
         <f t="shared" si="1"/>
         <v>-1.5</v>
       </c>
@@ -609,7 +634,7 @@
         <f t="shared" si="2"/>
         <v>1.9661051464753108</v>
       </c>
-      <c r="C9" s="1" t="str">
+      <c r="C9" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>=ERFC.PRECISE($A9)</v>
       </c>
@@ -617,8 +642,8 @@
         <v>1.9661051464753101</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
@@ -626,7 +651,7 @@
         <f t="shared" si="2"/>
         <v>1.8427007929497148</v>
       </c>
-      <c r="C10" s="1" t="str">
+      <c r="C10" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>=ERFC.PRECISE($A10)</v>
       </c>
@@ -634,8 +659,8 @@
         <v>1.8427007929497099</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
         <f t="shared" si="1"/>
         <v>-0.5</v>
       </c>
@@ -643,7 +668,7 @@
         <f t="shared" si="2"/>
         <v>1.5204998778130465</v>
       </c>
-      <c r="C11" s="1" t="str">
+      <c r="C11" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>=ERFC.PRECISE($A11)</v>
       </c>
@@ -651,8 +676,8 @@
         <v>1.5204998778129999</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -660,7 +685,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="C12" s="1" t="str">
+      <c r="C12" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>=ERFC.PRECISE($A12)</v>
       </c>
@@ -668,8 +693,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -677,7 +702,7 @@
         <f t="shared" si="2"/>
         <v>0.47950012218695348</v>
       </c>
-      <c r="C13" s="1" t="str">
+      <c r="C13" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>=ERFC.PRECISE($A13)</v>
       </c>
@@ -685,8 +710,8 @@
         <v>0.47950012218695298</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -694,7 +719,7 @@
         <f t="shared" si="2"/>
         <v>0.15729920705028513</v>
       </c>
-      <c r="C14" s="1" t="str">
+      <c r="C14" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>=ERFC.PRECISE($A14)</v>
       </c>
@@ -702,8 +727,8 @@
         <v>0.15729920705028499</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
         <f>A14+0.5</f>
         <v>1.5</v>
       </c>
@@ -711,7 +736,7 @@
         <f t="shared" si="2"/>
         <v>3.3894853524689267E-2</v>
       </c>
-      <c r="C15" s="1" t="str">
+      <c r="C15" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>=ERFC.PRECISE($A15)</v>
       </c>
@@ -719,8 +744,8 @@
         <v>3.3894853524689197E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -728,7 +753,7 @@
         <f t="shared" si="2"/>
         <v>4.6777349810472645E-3</v>
       </c>
-      <c r="C16" s="1" t="str">
+      <c r="C16" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>=ERFC.PRECISE($A16)</v>
       </c>
@@ -736,8 +761,8 @@
         <v>4.6777349810472602E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
@@ -745,7 +770,7 @@
         <f>_xlfn.ERFC.PRECISE($A17)</f>
         <v>4.0695201744495886E-4</v>
       </c>
-      <c r="C17" s="1" t="str">
+      <c r="C17" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>=ERFC.PRECISE($A17)</v>
       </c>
@@ -753,8 +778,8 @@
         <v>4.0695201744495897E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -762,7 +787,7 @@
         <f>_xlfn.ERFC.PRECISE($A18)</f>
         <v>2.2090496998585441E-5</v>
       </c>
-      <c r="C18" s="1" t="str">
+      <c r="C18" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>=ERFC.PRECISE($A18)</v>
       </c>
@@ -770,8 +795,8 @@
         <v>2.2090496998585401E-5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
         <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
@@ -779,7 +804,7 @@
         <f t="shared" ref="B19:B22" si="4">_xlfn.ERFC.PRECISE($A19)</f>
         <v>7.4309837234141288E-7</v>
       </c>
-      <c r="C19" s="1" t="str">
+      <c r="C19" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>=ERFC.PRECISE($A19)</v>
       </c>
@@ -787,8 +812,8 @@
         <v>7.4309837234141204E-7</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
         <f>A19+0.5</f>
         <v>4</v>
       </c>
@@ -796,7 +821,7 @@
         <f t="shared" si="4"/>
         <v>1.5417257900280017E-8</v>
       </c>
-      <c r="C20" s="1" t="str">
+      <c r="C20" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>=ERFC.PRECISE($A20)</v>
       </c>
@@ -804,8 +829,8 @@
         <v>1.541725790028E-8</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
         <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
@@ -813,7 +838,7 @@
         <f t="shared" si="4"/>
         <v>1.9661604415428865E-10</v>
       </c>
-      <c r="C21" s="1" t="str">
+      <c r="C21" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>=ERFC.PRECISE($A21)</v>
       </c>
@@ -821,8 +846,8 @@
         <v>1.9661604415428801E-10</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -830,7 +855,7 @@
         <f t="shared" si="4"/>
         <v>1.5374597944280339E-12</v>
       </c>
-      <c r="C22" s="1" t="str">
+      <c r="C22" s="2" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>=ERFC.PRECISE($A22)</v>
       </c>
@@ -838,89 +863,111 @@
         <v>1.537459794428E-12</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="4"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="4"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C25" s="10"/>
+      <c r="D25" s="9"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <f>_xlfn.ERFC.PRECISE(0.1)</f>
         <v>0.88753708398171505</v>
       </c>
-      <c r="B26" s="1" t="str">
+      <c r="B26" s="8" t="str">
         <f ca="1">_xlfn.FORMULATEXT(A26)</f>
         <v>=ERFC.PRECISE(0.1)</v>
       </c>
-      <c r="C26" s="4"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C26" s="7"/>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <f>_xlfn.ERFC.PRECISE(-0.1)</f>
         <v>1.1124629160182851</v>
       </c>
-      <c r="B27" s="1" t="str">
+      <c r="B27" s="8" t="str">
         <f ca="1">_xlfn.FORMULATEXT(A27)</f>
         <v>=ERFC.PRECISE(-0.1)</v>
       </c>
-      <c r="C27" s="4"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="C27" s="7"/>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="4"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="e">
+      <c r="D29" s="9"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="e">
         <f>_xlfn.ERFC.PRECISE(SQRT(-1))</f>
         <v>#NUM!</v>
       </c>
-      <c r="B30" s="1" t="str">
+      <c r="B30" s="8" t="str">
         <f ca="1">_xlfn.FORMULATEXT(A30)</f>
         <v>=ERFC.PRECISE(SQRT(-1))</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="e">
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="e">
         <f>_xlfn.ERFC.PRECISE("str")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="B31" s="1" t="str">
+      <c r="B31" s="8" t="str">
         <f t="shared" ref="B31:B32" ca="1" si="5">_xlfn.FORMULATEXT(A31)</f>
         <v>=ERFC.PRECISE("str")</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="e">
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="e">
         <f>_xlfn.ERFC.PRECISE(10/0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="B32" s="1" t="str">
+      <c r="B32" s="8" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>=ERFC.PRECISE(10/0)</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="8" t="s">
         <v>6</v>
       </c>
+      <c r="D32" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
